--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92338</v>
+        <v>92340</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99353</v>
+        <v>99359</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104073</v>
+        <v>104079</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92340</v>
+        <v>92342</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99359</v>
+        <v>99361</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104079</v>
+        <v>104081</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92342</v>
+        <v>92343</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99361</v>
+        <v>99362</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104081</v>
+        <v>104082</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92343</v>
+        <v>92349</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99362</v>
+        <v>99368</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104082</v>
+        <v>104088</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92349</v>
+        <v>92353</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99368</v>
+        <v>99372</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104088</v>
+        <v>104092</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99372</v>
+        <v>99374</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104092</v>
+        <v>104094</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92353</v>
+        <v>92355</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99374</v>
+        <v>99376</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104094</v>
+        <v>104096</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92355</v>
+        <v>92368</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136989540</v>
       </c>
       <c r="B3" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136989579</v>
       </c>
       <c r="B4" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136996592</v>
       </c>
       <c r="B5" t="n">
-        <v>58005</v>
+        <v>58018</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99376</v>
+        <v>99389</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104096</v>
+        <v>104109</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92368</v>
+        <v>92370</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136989540</v>
       </c>
       <c r="B3" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -902,7 +902,7 @@
         <v>136989579</v>
       </c>
       <c r="B4" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1019,7 +1019,7 @@
         <v>136996592</v>
       </c>
       <c r="B5" t="n">
-        <v>58018</v>
+        <v>58020</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1126,7 +1126,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1238,7 +1238,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1350,7 +1350,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99389</v>
+        <v>99391</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1462,7 +1462,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104109</v>
+        <v>104111</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -811,11 +811,7 @@
         </is>
       </c>
       <c r="I3" t="inlineStr"/>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M3" t="inlineStr"/>
       <c r="P3" t="inlineStr">
         <is>
           <t>Kvarnfallet, Dlr</t>
@@ -928,11 +924,7 @@
         </is>
       </c>
       <c r="I4" t="inlineStr"/>
-      <c r="M4" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
+      <c r="M4" t="inlineStr"/>
       <c r="P4" t="inlineStr">
         <is>
           <t>Kvarnfallet, Dlr</t>
@@ -1045,11 +1037,7 @@
         </is>
       </c>
       <c r="I5" t="inlineStr"/>
-      <c r="M5" t="inlineStr">
-        <is>
-          <t>färska spår</t>
-        </is>
-      </c>
+      <c r="M5" t="inlineStr"/>
       <c r="P5" t="inlineStr">
         <is>
           <t>Kvarnfallet, Dlr</t>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92370</v>
+        <v>92373</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99391</v>
+        <v>99394</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104111</v>
+        <v>104114</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92373</v>
+        <v>92383</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136989540</v>
       </c>
       <c r="B3" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136989579</v>
       </c>
       <c r="B4" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136996592</v>
       </c>
       <c r="B5" t="n">
-        <v>58020</v>
+        <v>58030</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99394</v>
+        <v>99404</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104114</v>
+        <v>104129</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92383</v>
+        <v>92384</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99404</v>
+        <v>99405</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104129</v>
+        <v>104130</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92384</v>
+        <v>92387</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136989540</v>
       </c>
       <c r="B3" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136989579</v>
       </c>
       <c r="B4" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136996592</v>
       </c>
       <c r="B5" t="n">
-        <v>58030</v>
+        <v>58031</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99405</v>
+        <v>99410</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104130</v>
+        <v>104135</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92387</v>
+        <v>92389</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99410</v>
+        <v>99412</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104135</v>
+        <v>104138</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92389</v>
+        <v>92394</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136989540</v>
       </c>
       <c r="B3" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136989579</v>
       </c>
       <c r="B4" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136996592</v>
       </c>
       <c r="B5" t="n">
-        <v>58031</v>
+        <v>58032</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99412</v>
+        <v>99418</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104138</v>
+        <v>104144</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104144</v>
+        <v>104145</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92394</v>
+        <v>92406</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99418</v>
+        <v>99430</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104145</v>
+        <v>104157</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92406</v>
+        <v>92407</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99430</v>
+        <v>99431</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104157</v>
+        <v>104158</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92407</v>
+        <v>92410</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99431</v>
+        <v>99434</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104158</v>
+        <v>104161</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92410</v>
+        <v>92411</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99434</v>
+        <v>99435</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104161</v>
+        <v>104162</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>

--- a/artfynd/A 35100-2026 artfynd.xlsx
+++ b/artfynd/A 35100-2026 artfynd.xlsx
@@ -683,7 +683,7 @@
         <v>136996576</v>
       </c>
       <c r="B2" t="n">
-        <v>92411</v>
+        <v>92414</v>
       </c>
       <c r="D2" t="inlineStr">
         <is>
@@ -785,7 +785,7 @@
         <v>136989540</v>
       </c>
       <c r="B3" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D3" t="inlineStr">
         <is>
@@ -898,7 +898,7 @@
         <v>136989579</v>
       </c>
       <c r="B4" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D4" t="inlineStr">
         <is>
@@ -1011,7 +1011,7 @@
         <v>136996592</v>
       </c>
       <c r="B5" t="n">
-        <v>58032</v>
+        <v>58035</v>
       </c>
       <c r="D5" t="inlineStr">
         <is>
@@ -1114,7 +1114,7 @@
         <v>136989351</v>
       </c>
       <c r="B6" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D6" t="inlineStr">
         <is>
@@ -1226,7 +1226,7 @@
         <v>136989393</v>
       </c>
       <c r="B7" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D7" t="inlineStr">
         <is>
@@ -1338,7 +1338,7 @@
         <v>136989738</v>
       </c>
       <c r="B8" t="n">
-        <v>99435</v>
+        <v>99438</v>
       </c>
       <c r="D8" t="inlineStr">
         <is>
@@ -1450,7 +1450,7 @@
         <v>136989462</v>
       </c>
       <c r="B9" t="n">
-        <v>104162</v>
+        <v>104166</v>
       </c>
       <c r="D9" t="inlineStr">
         <is>
